--- a/AAAGameData/Languages/ChineseTraditional.xlsx
+++ b/AAAGameData/Languages/ChineseTraditional.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>BRAKE</t>
   </si>
@@ -79,12 +79,15 @@
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>遊戲失敗</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
   </si>
   <si>
+    <t>返回</t>
+  </si>
+  <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
@@ -242,6 +245,9 @@
   </si>
   <si>
     <t>Victory</t>
+  </si>
+  <si>
+    <t>遊戲勝利</t>
   </si>
 </sst>
 </file>
@@ -423,6 +429,502 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -4504,250 +5006,250 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4762,7 +5264,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId273" name="A1">
+            <control shapeId="1056" r:id="rId393" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4784,7 +5286,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId274" name="A2">
+            <control shapeId="1057" r:id="rId394" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4806,7 +5308,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId275" name="A3">
+            <control shapeId="1058" r:id="rId395" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4828,7 +5330,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId276" name="A4">
+            <control shapeId="1059" r:id="rId396" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4850,7 +5352,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId277" name="A5">
+            <control shapeId="1060" r:id="rId397" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4872,7 +5374,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId278" name="A6">
+            <control shapeId="1061" r:id="rId398" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4894,7 +5396,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId279" name="A7">
+            <control shapeId="1062" r:id="rId399" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4916,7 +5418,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId280" name="A8">
+            <control shapeId="1063" r:id="rId400" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4938,7 +5440,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId281" name="A9">
+            <control shapeId="1064" r:id="rId401" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4960,7 +5462,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId282" name="A10">
+            <control shapeId="1065" r:id="rId402" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4982,7 +5484,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId283" name="A11">
+            <control shapeId="1066" r:id="rId403" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5004,7 +5506,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId284" name="A12">
+            <control shapeId="1067" r:id="rId404" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5026,7 +5528,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId285" name="A13">
+            <control shapeId="1068" r:id="rId405" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5048,7 +5550,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId286" name="A14">
+            <control shapeId="1069" r:id="rId406" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5070,7 +5572,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId287" name="A15">
+            <control shapeId="1070" r:id="rId407" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5092,7 +5594,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId288" name="A16">
+            <control shapeId="1071" r:id="rId408" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5114,7 +5616,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId289" name="A17">
+            <control shapeId="1072" r:id="rId409" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5136,7 +5638,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId290" name="A18">
+            <control shapeId="1073" r:id="rId410" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5158,7 +5660,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId291" name="A19">
+            <control shapeId="1074" r:id="rId411" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5180,7 +5682,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId292" name="A20">
+            <control shapeId="1075" r:id="rId412" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5202,7 +5704,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId293" name="A21">
+            <control shapeId="1076" r:id="rId413" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5224,7 +5726,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId294" name="A22">
+            <control shapeId="1077" r:id="rId414" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5246,7 +5748,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId295" name="A23">
+            <control shapeId="1078" r:id="rId415" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5268,7 +5770,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId296" name="A24">
+            <control shapeId="1079" r:id="rId416" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5290,7 +5792,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId297" name="A25">
+            <control shapeId="1080" r:id="rId417" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5312,7 +5814,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId298" name="A26">
+            <control shapeId="1081" r:id="rId418" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5334,7 +5836,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId299" name="A27">
+            <control shapeId="1082" r:id="rId419" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5356,7 +5858,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId300" name="A28">
+            <control shapeId="1083" r:id="rId420" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5378,7 +5880,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId301" name="A29">
+            <control shapeId="1084" r:id="rId421" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5400,7 +5902,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId302" name="A30">
+            <control shapeId="1085" r:id="rId422" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5422,7 +5924,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId303" name="A31">
+            <control shapeId="1086" r:id="rId423" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/AAAGameData/Languages/ChineseTraditional.xlsx
+++ b/AAAGameData/Languages/ChineseTraditional.xlsx
@@ -62,66 +62,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
-    <t>BRAKE</t>
+    <t>NoSaveData</t>
   </si>
   <si>
-    <t>刹車</t>
-  </si>
-  <si>
-    <t>ENGINE</t>
-  </si>
-  <si>
-    <t>引擎</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>遊戲失敗</t>
-  </si>
-  <si>
-    <t>GameOverUIForm.Back</t>
-  </si>
-  <si>
-    <t>返回</t>
-  </si>
-  <si>
-    <t>Level.DisplayName1</t>
-  </si>
-  <si>
-    <t>關卡1名字</t>
-  </si>
-  <si>
-    <t>Level.DisplayName2</t>
-  </si>
-  <si>
-    <t>關卡2名字</t>
-  </si>
-  <si>
-    <t>Level.DisplayName3</t>
-  </si>
-  <si>
-    <t>關卡3名字</t>
-  </si>
-  <si>
-    <t>Level.DisplayName4</t>
-  </si>
-  <si>
-    <t>關卡4名字</t>
-  </si>
-  <si>
-    <t>Level.DisplayName5</t>
-  </si>
-  <si>
-    <t>關卡5名字</t>
-  </si>
-  <si>
-    <t>MenuUIForm.Tips</t>
-  </si>
-  <si>
-    <t>點擊開始</t>
+    <t/>
   </si>
   <si>
     <t>Nothing</t>
@@ -142,34 +88,10 @@
     <t>開</t>
   </si>
   <si>
-    <t>RatingDialog.CancelTxt</t>
+    <t>OpenSaveList</t>
   </si>
   <si>
-    <t>取消</t>
-  </si>
-  <si>
-    <t>RatingDialog.Description</t>
-  </si>
-  <si>
-    <t>喜歡這款遊戲嗎？ \n請給個5星好評吧！</t>
-  </si>
-  <si>
-    <t>RatingDialog.HighRatingTips</t>
-  </si>
-  <si>
-    <t>感謝您的肯定！ 我們將再接再厲！</t>
-  </si>
-  <si>
-    <t>RatingDialog.LowRatingTips</t>
-  </si>
-  <si>
-    <t>感謝您的評估，我們盡力完善優化！</t>
-  </si>
-  <si>
-    <t>RatingDialog.RateTxt</t>
-  </si>
-  <si>
-    <t>評星</t>
+    <t>打開保存清單</t>
   </si>
   <si>
     <t>Settings.Help</t>
@@ -220,16 +142,10 @@
     <t>震動</t>
   </si>
   <si>
-    <t>SHOP</t>
+    <t>Story_Welcome</t>
   </si>
   <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>STEERING</t>
-  </si>
-  <si>
-    <t>駕駛</t>
+    <t>歡迎來到諸神之戰的世界。 在這裡，你將扮演一比特英雄，踏上史詩般的冒險旅程。 準備好開始你的傳奇了嗎？</t>
   </si>
   <si>
     <t>TermsOfService</t>
@@ -238,16 +154,28 @@
     <t>服務條款</t>
   </si>
   <si>
-    <t>UNLOCK</t>
+    <t>UI_Continue</t>
   </si>
   <si>
-    <t>解鎖</t>
+    <t>繼續</t>
   </si>
   <si>
-    <t>Victory</t>
+    <t>UI_InputName</t>
   </si>
   <si>
-    <t>遊戲勝利</t>
+    <t>請輸入你的名字</t>
+  </si>
+  <si>
+    <t>UI_PressSpace</t>
+  </si>
+  <si>
+    <t>按空白鍵繼續</t>
+  </si>
+  <si>
+    <t>UI_Welcome</t>
+  </si>
+  <si>
+    <t>歡迎你，{0}！</t>
   </si>
 </sst>
 </file>
@@ -324,7 +252,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -332,7 +260,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -340,7 +268,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -351,55 +279,7 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -2034,6 +1914,794 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2050,7 +2718,1039 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1056">
+            <xdr:cNvPr hidden="1" name="A1" id="1044">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1044"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A2" id="1045">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1045"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A3" id="1046">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1046"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A4" id="1047">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1047"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A5" id="1048">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1048"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A6" id="1049">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1049"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A7" id="1050">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1050"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A8" id="1051">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1051"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A9" id="1052">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1052"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A10" id="1053">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1053"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A11" id="1054">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1054"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A12" id="1055">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1055"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A13" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -2125,18 +3825,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1057">
+            <xdr:cNvPr hidden="1" name="A14" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -2211,18 +3911,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1058">
+            <xdr:cNvPr hidden="1" name="A15" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -2297,18 +3997,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1059">
+            <xdr:cNvPr hidden="1" name="A16" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -2383,18 +4083,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1060">
+            <xdr:cNvPr hidden="1" name="A17" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -2469,18 +4169,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1061">
+            <xdr:cNvPr hidden="1" name="A18" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -2555,1038 +4255,6 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1062">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1063">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1064">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1065">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1066">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1067">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1068">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1069">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1070">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1071">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1072">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1073">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -3598,1042 +4266,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1074">
+            <xdr:cNvPr hidden="1" name="A19" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1075">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1076">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1077">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1078">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1079">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1080">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1081">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1082">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1083">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1084">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1085">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1086">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4965,12 +4601,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.4074859619141" customWidth="1"/>
-    <col min="3" max="3" width="42.2229309082031" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5144,114 +4780,6 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5264,7 +4792,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId393" name="A1">
+            <control shapeId="1044" r:id="rId579" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5286,7 +4814,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId394" name="A2">
+            <control shapeId="1045" r:id="rId580" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5308,7 +4836,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId395" name="A3">
+            <control shapeId="1046" r:id="rId581" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5330,7 +4858,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId396" name="A4">
+            <control shapeId="1047" r:id="rId582" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5352,7 +4880,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId397" name="A5">
+            <control shapeId="1048" r:id="rId583" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5374,7 +4902,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId398" name="A6">
+            <control shapeId="1049" r:id="rId584" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5396,7 +4924,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId399" name="A7">
+            <control shapeId="1050" r:id="rId585" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5418,7 +4946,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId400" name="A8">
+            <control shapeId="1051" r:id="rId586" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5440,7 +4968,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId401" name="A9">
+            <control shapeId="1052" r:id="rId587" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5462,7 +4990,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId402" name="A10">
+            <control shapeId="1053" r:id="rId588" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5484,7 +5012,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId403" name="A11">
+            <control shapeId="1054" r:id="rId589" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5506,7 +5034,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId404" name="A12">
+            <control shapeId="1055" r:id="rId590" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5528,7 +5056,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId405" name="A13">
+            <control shapeId="1056" r:id="rId591" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5550,7 +5078,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId406" name="A14">
+            <control shapeId="1057" r:id="rId592" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5572,7 +5100,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId407" name="A15">
+            <control shapeId="1058" r:id="rId593" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5594,7 +5122,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId408" name="A16">
+            <control shapeId="1059" r:id="rId594" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5616,7 +5144,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId409" name="A17">
+            <control shapeId="1060" r:id="rId595" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5638,7 +5166,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId410" name="A18">
+            <control shapeId="1061" r:id="rId596" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5660,7 +5188,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId411" name="A19">
+            <control shapeId="1062" r:id="rId597" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5680,270 +5208,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId412" name="A20">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId413" name="A21">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId414" name="A22">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId415" name="A23">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId416" name="A24">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId417" name="A25">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId418" name="A26">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId419" name="A27">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId420" name="A28">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId421" name="A29">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId422" name="A30">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId423" name="A31">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>31</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/ChineseTraditional.xlsx
+++ b/AAAGameData/Languages/ChineseTraditional.xlsx
@@ -62,12 +62,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>NoSaveData</t>
   </si>
   <si>
-    <t/>
+    <t>沒有存檔數據</t>
   </si>
   <si>
     <t>Nothing</t>
@@ -92,6 +92,30 @@
   </si>
   <si>
     <t>打開保存清單</t>
+  </si>
+  <si>
+    <t>scene.base.name</t>
+  </si>
+  <si>
+    <t>基地</t>
+  </si>
+  <si>
+    <t>scene.menu.name</t>
+  </si>
+  <si>
+    <t>主菜單</t>
+  </si>
+  <si>
+    <t>scene.tutorial.name</t>
+  </si>
+  <si>
+    <t>某個實驗室</t>
+  </si>
+  <si>
+    <t>scene.world.name</t>
+  </si>
+  <si>
+    <t>大世界</t>
   </si>
   <si>
     <t>Settings.Help</t>
@@ -252,7 +276,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -260,7 +284,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -276,6 +300,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -2702,6 +2742,358 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2718,351 +3110,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1044">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1044"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1045">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1046">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1047">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1047"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1048">
+            <xdr:cNvPr hidden="1" name="A1" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1048"/>
@@ -3137,18 +3185,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1049">
+            <xdr:cNvPr hidden="1" name="A2" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1049"/>
@@ -3223,18 +3271,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1050">
+            <xdr:cNvPr hidden="1" name="A3" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1050"/>
@@ -3309,18 +3357,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1051">
+            <xdr:cNvPr hidden="1" name="A4" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1051"/>
@@ -3395,18 +3443,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1052">
+            <xdr:cNvPr hidden="1" name="A5" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1052"/>
@@ -3481,18 +3529,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1053">
+            <xdr:cNvPr hidden="1" name="A6" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1053"/>
@@ -3567,18 +3615,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1054">
+            <xdr:cNvPr hidden="1" name="A7" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1054"/>
@@ -3653,18 +3701,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1055">
+            <xdr:cNvPr hidden="1" name="A8" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -3739,18 +3787,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1056">
+            <xdr:cNvPr hidden="1" name="A9" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -3825,18 +3873,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1057">
+            <xdr:cNvPr hidden="1" name="A10" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -3911,18 +3959,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1058">
+            <xdr:cNvPr hidden="1" name="A11" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -3997,18 +4045,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1059">
+            <xdr:cNvPr hidden="1" name="A12" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -4083,18 +4131,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1060">
+            <xdr:cNvPr hidden="1" name="A13" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -4169,18 +4217,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1061">
+            <xdr:cNvPr hidden="1" name="A14" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -4255,6 +4303,350 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A15" id="1062">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1062"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1063">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1064">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1065">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -4266,10 +4658,354 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1062">
+            <xdr:cNvPr hidden="1" name="A19" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1067">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1067"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1068">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1068"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1069">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4601,7 +5337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -4780,6 +5516,42 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1"/>
+      <c r="B20" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1"/>
+      <c r="B22" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1"/>
+      <c r="B23" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4792,7 +5564,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1044" r:id="rId579" name="A1">
+            <control shapeId="1048" r:id="rId663" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4814,7 +5586,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId580" name="A2">
+            <control shapeId="1049" r:id="rId664" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4836,7 +5608,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId581" name="A3">
+            <control shapeId="1050" r:id="rId665" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4858,7 +5630,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId582" name="A4">
+            <control shapeId="1051" r:id="rId666" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4880,7 +5652,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId583" name="A5">
+            <control shapeId="1052" r:id="rId667" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4902,7 +5674,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId584" name="A6">
+            <control shapeId="1053" r:id="rId668" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4924,7 +5696,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId585" name="A7">
+            <control shapeId="1054" r:id="rId669" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4946,7 +5718,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId586" name="A8">
+            <control shapeId="1055" r:id="rId670" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4968,7 +5740,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId587" name="A9">
+            <control shapeId="1056" r:id="rId671" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4990,7 +5762,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId588" name="A10">
+            <control shapeId="1057" r:id="rId672" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5012,7 +5784,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId589" name="A11">
+            <control shapeId="1058" r:id="rId673" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5034,7 +5806,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId590" name="A12">
+            <control shapeId="1059" r:id="rId674" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5056,7 +5828,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId591" name="A13">
+            <control shapeId="1060" r:id="rId675" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5078,7 +5850,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId592" name="A14">
+            <control shapeId="1061" r:id="rId676" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5100,7 +5872,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId593" name="A15">
+            <control shapeId="1062" r:id="rId677" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5122,7 +5894,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId594" name="A16">
+            <control shapeId="1063" r:id="rId678" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5144,7 +5916,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId595" name="A17">
+            <control shapeId="1064" r:id="rId679" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5166,7 +5938,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId596" name="A18">
+            <control shapeId="1065" r:id="rId680" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5188,7 +5960,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId597" name="A19">
+            <control shapeId="1066" r:id="rId681" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5208,6 +5980,94 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1067" r:id="rId682" name="A20">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1068" r:id="rId683" name="A21">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1069" r:id="rId684" name="A22">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1070" r:id="rId685" name="A23">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/ChineseTraditional.xlsx
+++ b/AAAGameData/Languages/ChineseTraditional.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>NoSaveData</t>
   </si>
@@ -94,16 +94,58 @@
     <t>打開保存清單</t>
   </si>
   <si>
+    <t>scene.abyss.name</t>
+  </si>
+  <si>
+    <t>深淵之地</t>
+  </si>
+  <si>
+    <t>scene.avalon.name</t>
+  </si>
+  <si>
+    <t>阿瓦隆</t>
+  </si>
+  <si>
+    <t>scene.babylon.name</t>
+  </si>
+  <si>
+    <t>巴比倫空中花園</t>
+  </si>
+  <si>
     <t>scene.base.name</t>
   </si>
   <si>
     <t>基地</t>
   </si>
   <si>
+    <t>scene.herheim.name</t>
+  </si>
+  <si>
+    <t>赫爾海默</t>
+  </si>
+  <si>
     <t>scene.menu.name</t>
   </si>
   <si>
     <t>主菜單</t>
+  </si>
+  <si>
+    <t>scene.olympus.name</t>
+  </si>
+  <si>
+    <t>奧林匹斯山</t>
+  </si>
+  <si>
+    <t>scene.takamahara.name</t>
+  </si>
+  <si>
+    <t>高天原</t>
+  </si>
+  <si>
+    <t>scene.tiangong.name</t>
+  </si>
+  <si>
+    <t>天宮</t>
   </si>
   <si>
     <t>scene.tutorial.name</t>
@@ -260,7 +302,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -268,15 +310,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -292,7 +334,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -304,7 +346,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
@@ -312,14 +354,42 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -332,15 +402,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -349,6 +419,338 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -3110,609 +3512,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1048">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1048"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1049">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1049"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1050">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1050"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1051">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1051"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1052">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1052"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1053">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1053"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1054">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1054"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1055">
+            <xdr:cNvPr hidden="1" name="A1" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -3787,18 +3587,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1056">
+            <xdr:cNvPr hidden="1" name="A2" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -3873,18 +3673,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1057">
+            <xdr:cNvPr hidden="1" name="A3" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -3959,18 +3759,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1058">
+            <xdr:cNvPr hidden="1" name="A4" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -4045,18 +3845,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1059">
+            <xdr:cNvPr hidden="1" name="A5" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -4131,18 +3931,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1060">
+            <xdr:cNvPr hidden="1" name="A6" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -4217,18 +4017,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1061">
+            <xdr:cNvPr hidden="1" name="A7" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -4303,18 +4103,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1062">
+            <xdr:cNvPr hidden="1" name="A8" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -4389,18 +4189,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1063">
+            <xdr:cNvPr hidden="1" name="A9" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -4475,18 +4275,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1064">
+            <xdr:cNvPr hidden="1" name="A10" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -4561,18 +4361,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1065">
+            <xdr:cNvPr hidden="1" name="A11" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -4647,18 +4447,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1066">
+            <xdr:cNvPr hidden="1" name="A12" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -4733,18 +4533,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1067">
+            <xdr:cNvPr hidden="1" name="A13" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -4819,18 +4619,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1068">
+            <xdr:cNvPr hidden="1" name="A14" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -4905,18 +4705,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1069">
+            <xdr:cNvPr hidden="1" name="A15" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -4991,6 +4791,608 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1071">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1071"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1072">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1072"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1073">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1074">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1075">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1076">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -5002,10 +5404,612 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1070">
+            <xdr:cNvPr hidden="1" name="A23" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A24" id="1078">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A25" id="1079">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A26" id="1080">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A27" id="1081">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A28" id="1082">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A29" id="1083">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A30" id="1084">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5337,11 +6341,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.2728118896484" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5552,6 +6556,69 @@
         <v>45</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1"/>
+      <c r="B24" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1"/>
+      <c r="B26" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1"/>
+      <c r="B27" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1"/>
+      <c r="B28" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1"/>
+      <c r="B29" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1"/>
+      <c r="B30" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5564,7 +6631,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId663" name="A1">
+            <control shapeId="1055" r:id="rId743" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5586,7 +6653,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId664" name="A2">
+            <control shapeId="1056" r:id="rId744" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5608,7 +6675,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId665" name="A3">
+            <control shapeId="1057" r:id="rId745" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5630,7 +6697,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId666" name="A4">
+            <control shapeId="1058" r:id="rId746" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5652,7 +6719,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId667" name="A5">
+            <control shapeId="1059" r:id="rId747" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5674,7 +6741,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId668" name="A6">
+            <control shapeId="1060" r:id="rId748" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5696,7 +6763,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId669" name="A7">
+            <control shapeId="1061" r:id="rId749" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5718,7 +6785,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId670" name="A8">
+            <control shapeId="1062" r:id="rId750" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5740,7 +6807,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId671" name="A9">
+            <control shapeId="1063" r:id="rId751" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5762,7 +6829,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId672" name="A10">
+            <control shapeId="1064" r:id="rId752" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5784,7 +6851,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId673" name="A11">
+            <control shapeId="1065" r:id="rId753" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5806,7 +6873,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId674" name="A12">
+            <control shapeId="1066" r:id="rId754" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5828,7 +6895,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId675" name="A13">
+            <control shapeId="1067" r:id="rId755" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5850,7 +6917,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId676" name="A14">
+            <control shapeId="1068" r:id="rId756" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5872,7 +6939,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId677" name="A15">
+            <control shapeId="1069" r:id="rId757" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5894,7 +6961,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId678" name="A16">
+            <control shapeId="1070" r:id="rId758" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5916,7 +6983,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId679" name="A17">
+            <control shapeId="1071" r:id="rId759" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5938,7 +7005,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId680" name="A18">
+            <control shapeId="1072" r:id="rId760" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5960,7 +7027,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId681" name="A19">
+            <control shapeId="1073" r:id="rId761" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5982,7 +7049,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId682" name="A20">
+            <control shapeId="1074" r:id="rId762" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6004,7 +7071,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId683" name="A21">
+            <control shapeId="1075" r:id="rId763" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6026,7 +7093,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId684" name="A22">
+            <control shapeId="1076" r:id="rId764" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6048,7 +7115,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId685" name="A23">
+            <control shapeId="1077" r:id="rId765" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6068,6 +7135,160 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1078" r:id="rId766" name="A24">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1079" r:id="rId767" name="A25">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1080" r:id="rId768" name="A26">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1081" r:id="rId769" name="A27">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1082" r:id="rId770" name="A28">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1083" r:id="rId771" name="A29">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1084" r:id="rId772" name="A30">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>
